--- a/sheets/대금율보/검수/엄마야 누나야.xlsx
+++ b/sheets/대금율보/검수/엄마야 누나야.xlsx
@@ -2334,20 +2334,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="43.01" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="63.87" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="63.87" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="63.87" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="63.87" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="63.87" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="63.87" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="63.87" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="63.87" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="63.87" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="63.87" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="63.87" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -2807,7 +2807,7 @@
       <c r="H13" s="21"/>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="63.87" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -2844,6 +2844,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="93"/>
 </worksheet>
 </file>